--- a/tests.xlsx
+++ b/tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17EBC574-6C99-484D-B181-D7070F42257B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1428AC53-C0C6-4855-9D57-9870963003CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7200" yWindow="885" windowWidth="21600" windowHeight="11385" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tests" sheetId="1" r:id="rId1"/>
@@ -29,99 +29,150 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="48">
   <si>
     <t>id</t>
   </si>
   <si>
-    <t>название теста</t>
-  </si>
-  <si>
-    <t>изображение</t>
-  </si>
-  <si>
-    <t>автор</t>
-  </si>
-  <si>
-    <t>дата</t>
-  </si>
-  <si>
-    <t>время</t>
-  </si>
-  <si>
-    <t>Тест 1</t>
-  </si>
-  <si>
-    <t>1.jpg</t>
-  </si>
-  <si>
-    <t>Дмитрий</t>
-  </si>
-  <si>
-    <t>Тест 2</t>
-  </si>
-  <si>
-    <t>2.jpg</t>
-  </si>
-  <si>
-    <t>id теста</t>
-  </si>
-  <si>
-    <t>вопрос</t>
-  </si>
-  <si>
-    <t>ответ 1</t>
-  </si>
-  <si>
-    <t>ответ 2</t>
-  </si>
-  <si>
-    <t>ответ 3</t>
-  </si>
-  <si>
-    <t>ответ 4</t>
-  </si>
-  <si>
-    <t>ответ 5</t>
-  </si>
-  <si>
-    <t>ответ 6</t>
-  </si>
-  <si>
-    <t>Столица Франции?</t>
-  </si>
-  <si>
-    <t>Париж</t>
-  </si>
-  <si>
-    <t>Лондон</t>
-  </si>
-  <si>
-    <t>Тюмень</t>
-  </si>
-  <si>
-    <t>Берлин</t>
-  </si>
-  <si>
-    <t>Стамбул</t>
-  </si>
-  <si>
-    <t>Москва</t>
-  </si>
-  <si>
-    <t>2+2?</t>
-  </si>
-  <si>
-    <t>99+1</t>
-  </si>
-  <si>
-    <t>85-5</t>
-  </si>
-  <si>
-    <t>текстовый ответ</t>
-  </si>
-  <si>
-    <t>Столица России?</t>
+    <t>title</t>
+  </si>
+  <si>
+    <t>image</t>
+  </si>
+  <si>
+    <t>author</t>
+  </si>
+  <si>
+    <t>date</t>
+  </si>
+  <si>
+    <t>time_limit</t>
+  </si>
+  <si>
+    <t>HTML базовый</t>
+  </si>
+  <si>
+    <t>img/html_test.jpg</t>
+  </si>
+  <si>
+    <t>Иванов И.И.</t>
+  </si>
+  <si>
+    <t>CSS селекторы</t>
+  </si>
+  <si>
+    <t>img/css_test.jpg</t>
+  </si>
+  <si>
+    <t>Петров П.П.</t>
+  </si>
+  <si>
+    <t>test_id</t>
+  </si>
+  <si>
+    <t>question</t>
+  </si>
+  <si>
+    <t>answer1</t>
+  </si>
+  <si>
+    <t>answer2</t>
+  </si>
+  <si>
+    <t>answer3</t>
+  </si>
+  <si>
+    <t>answer4</t>
+  </si>
+  <si>
+    <t>answer5</t>
+  </si>
+  <si>
+    <t>answer6</t>
+  </si>
+  <si>
+    <t>text_answer</t>
+  </si>
+  <si>
+    <t>Какой тег для заголовка 1 уровня?</t>
+  </si>
+  <si>
+    <t>h1</t>
+  </si>
+  <si>
+    <t>h2</t>
+  </si>
+  <si>
+    <t>head</t>
+  </si>
+  <si>
+    <t>header</t>
+  </si>
+  <si>
+    <t>Какой тег для абзаца?</t>
+  </si>
+  <si>
+    <t>p</t>
+  </si>
+  <si>
+    <t>div</t>
+  </si>
+  <si>
+    <t>span</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>br</t>
+  </si>
+  <si>
+    <t>Сколько уровней заголовков в HTML?</t>
+  </si>
+  <si>
+    <t>Как расшифровывается HTML?</t>
+  </si>
+  <si>
+    <t>HyperText Markup Language</t>
+  </si>
+  <si>
+    <t>Как выбрать элемент по id?</t>
+  </si>
+  <si>
+    <t>#id</t>
+  </si>
+  <si>
+    <t>.id</t>
+  </si>
+  <si>
+    <t>*id</t>
+  </si>
+  <si>
+    <t>$id</t>
+  </si>
+  <si>
+    <t>@id</t>
+  </si>
+  <si>
+    <t>Как выбрать класс?</t>
+  </si>
+  <si>
+    <t>.class</t>
+  </si>
+  <si>
+    <t>#class</t>
+  </si>
+  <si>
+    <t>class</t>
+  </si>
+  <si>
+    <t>*class</t>
+  </si>
+  <si>
+    <t>$class</t>
+  </si>
+  <si>
+    <t>@class</t>
   </si>
 </sst>
 </file>
@@ -482,10 +533,10 @@
         <v>8</v>
       </c>
       <c r="E2" s="1">
-        <v>46134</v>
+        <v>45306</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -499,13 +550,13 @@
         <v>10</v>
       </c>
       <c r="D3" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="E3" s="1">
-        <v>46134</v>
+        <v>45342</v>
       </c>
       <c r="F3">
-        <v>5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -515,10 +566,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BB657B04-9919-4F2B-850C-F98D9868800D}">
-  <dimension ref="A1:J6"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="3" max="3" width="20" customWidth="1"/>
+    <col min="9" max="9" width="14.140625" customWidth="1"/>
+    <col min="10" max="10" width="15.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
@@ -526,31 +579,31 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="C1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="H1" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J1" t="s">
-        <v>29</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -561,24 +614,18 @@
         <v>1</v>
       </c>
       <c r="C2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="D2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="E2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="F2" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G2" t="s">
-        <v>23</v>
-      </c>
-      <c r="H2" t="s">
-        <v>24</v>
-      </c>
-      <c r="I2" t="s">
         <v>25</v>
       </c>
     </row>
@@ -592,23 +639,20 @@
       <c r="C3" t="s">
         <v>26</v>
       </c>
-      <c r="D3">
-        <v>4</v>
-      </c>
-      <c r="E3">
-        <v>2</v>
-      </c>
-      <c r="F3">
-        <v>6</v>
-      </c>
-      <c r="G3">
-        <v>8</v>
-      </c>
-      <c r="H3">
-        <v>7</v>
-      </c>
-      <c r="I3">
-        <v>99</v>
+      <c r="D3" t="s">
+        <v>27</v>
+      </c>
+      <c r="E3" t="s">
+        <v>28</v>
+      </c>
+      <c r="F3" t="s">
+        <v>29</v>
+      </c>
+      <c r="G3" t="s">
+        <v>30</v>
+      </c>
+      <c r="H3" t="s">
+        <v>31</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
@@ -616,22 +660,25 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="D4">
-        <v>100</v>
+        <v>6</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G4">
-        <v>5</v>
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
@@ -639,19 +686,13 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>28</v>
-      </c>
-      <c r="D5">
-        <v>80</v>
-      </c>
-      <c r="E5">
         <v>33</v>
       </c>
-      <c r="F5">
-        <v>9</v>
+      <c r="J5" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
@@ -662,10 +703,54 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>30</v>
-      </c>
-      <c r="J6" t="s">
-        <v>25</v>
+        <v>35</v>
+      </c>
+      <c r="D6" t="s">
+        <v>36</v>
+      </c>
+      <c r="E6" t="s">
+        <v>37</v>
+      </c>
+      <c r="F6" t="s">
+        <v>0</v>
+      </c>
+      <c r="G6" t="s">
+        <v>38</v>
+      </c>
+      <c r="H6" t="s">
+        <v>39</v>
+      </c>
+      <c r="I6" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A7">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>2</v>
+      </c>
+      <c r="C7" t="s">
+        <v>41</v>
+      </c>
+      <c r="D7" t="s">
+        <v>42</v>
+      </c>
+      <c r="E7" t="s">
+        <v>43</v>
+      </c>
+      <c r="F7" t="s">
+        <v>44</v>
+      </c>
+      <c r="G7" t="s">
+        <v>45</v>
+      </c>
+      <c r="H7" t="s">
+        <v>46</v>
+      </c>
+      <c r="I7" t="s">
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/tests.xlsx
+++ b/tests.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Dima\Desktop\Справочник\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1428AC53-C0C6-4855-9D57-9870963003CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{719CBB16-B4D0-4400-A544-36323C9C42CA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="14400" windowHeight="15600" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="885" windowWidth="21600" windowHeight="11385" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="tests" sheetId="1" r:id="rId1"/>
@@ -541,7 +541,7 @@
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="B3" t="s">
         <v>9</v>
